--- a/output/pdf_financials_xlsx/AUEX.xlsx
+++ b/output/pdf_financials_xlsx/AUEX.xlsx
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.084176</v>
+        <v>0.275832</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.188239</v>
+        <v>0.282741</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.12471</v>
+        <v>0.294447</v>
       </c>
     </row>
     <row r="11">
@@ -593,13 +593,13 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.084176</v>
+        <v>-0.275832</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.188239</v>
+        <v>-0.282741</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.12471</v>
+        <v>-0.294447</v>
       </c>
     </row>
     <row r="12">
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.140204</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.04386</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.033887</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.140204</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.04386</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.072917</v>
+        <v>0.106804</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.16157</v>
+        <v>0.021366</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.059305</v>
+        <v>0.015445</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.357544</v>
+        <v>0.323657</v>
       </c>
     </row>
     <row r="49">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5858,17 +5858,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E99" s="5" t="n">
         <v>0.275832</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>-0.282741</v>
+        <v>0.282741</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.294447</v>
+        <v>0.294447</v>
       </c>
     </row>
     <row r="100">
@@ -5945,7 +5945,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">

--- a/output/pdf_financials_xlsx/AUEX.xlsx
+++ b/output/pdf_financials_xlsx/AUEX.xlsx
@@ -4646,7 +4646,11 @@
           <t>Subscription received for private placement 30,000</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
